--- a/nriss-patch-2/ig/StructureDefinition-fr-device-request-document.xlsx
+++ b/nriss-patch-2/ig/StructureDefinition-fr-device-request-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-27T15:58:47+00:00</t>
+    <t>2026-08-04T07:44:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nriss-patch-2/ig/StructureDefinition-fr-device-request-document.xlsx
+++ b/nriss-patch-2/ig/StructureDefinition-fr-device-request-document.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$70</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$67</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2600" uniqueCount="532">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2490" uniqueCount="520">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-04T07:44:41+00:00</t>
+    <t>2026-08-07T09:15:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1525,56 +1525,17 @@
     <t>DeviceRequest.reasonReference</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Condition|4.0.1|Observation|4.0.1|DiagnosticReport|4.0.1|DocumentReference|4.0.1)
+    <t xml:space="preserve">Reference(Observation|4.0.1|https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-condition-document|0.1.0|https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-observation-prevention-document|0.1.0|https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-observation-ald-document|0.1.0|https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-observation-work-related-accident-document|0.1.0)
 </t>
   </si>
   <si>
-    <t>Raisons liées au DM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">value:resolve().code}
-</t>
+    <t>Raisons liées à l'utilisation du dispositif médical</t>
   </si>
   <si>
     <t>Request.reasonReference</t>
   </si>
   <si>
     <t>.outboundRelationship[typeCode=RSON].target</t>
-  </si>
-  <si>
-    <t>DeviceRequest.reasonReference:EnRapportAvecALD</t>
-  </si>
-  <si>
-    <t>EnRapportAvecALD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-condition-document|0.1.0)
-</t>
-  </si>
-  <si>
-    <t>En rapport avec une Affection Longue Durée (ALD)</t>
-  </si>
-  <si>
-    <t>DeviceRequest.reasonReference:EnRapportAvecAccidentTravail</t>
-  </si>
-  <si>
-    <t>EnRapportAvecAccidentTravail</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-observation-work-related-accident-document|0.1.0)
-</t>
-  </si>
-  <si>
-    <t>En rapport avec accident travail</t>
-  </si>
-  <si>
-    <t>DeviceRequest.reasonReference:EnRapportAvecLaPrevention</t>
-  </si>
-  <si>
-    <t>EnRapportAvecLaPrevention</t>
-  </si>
-  <si>
-    <t>En rapport avec la prévention</t>
   </si>
   <si>
     <t>DeviceRequest.insurance</t>
@@ -1983,12 +1944,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO70"/>
+  <dimension ref="A1:AO67"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="56.140625" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="41.48046875" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="25.1484375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="15.02734375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
@@ -1996,7 +1957,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="126.609375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="255.0" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -9236,7 +9197,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="63" hidden="true">
+    <row r="63">
       <c r="A63" t="s" s="2">
         <v>486</v>
       </c>
@@ -9309,14 +9270,16 @@
         <v>78</v>
       </c>
       <c r="AB63" t="s" s="2">
-        <v>489</v>
-      </c>
-      <c r="AC63" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="AC63" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="AD63" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE63" t="s" s="2">
-        <v>138</v>
+        <v>78</v>
       </c>
       <c r="AF63" t="s" s="2">
         <v>486</v>
@@ -9334,13 +9297,13 @@
         <v>101</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="AL63" t="s" s="2">
         <v>482</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>484</v>
@@ -9349,16 +9312,14 @@
         <v>78</v>
       </c>
     </row>
-    <row r="64">
+    <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>486</v>
-      </c>
-      <c r="C64" t="s" s="2">
-        <v>493</v>
-      </c>
+        <v>491</v>
+      </c>
+      <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
         <v>78</v>
       </c>
@@ -9367,25 +9328,25 @@
         <v>79</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H64" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="I64" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K64" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="L64" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="M64" t="s" s="2">
         <v>494</v>
-      </c>
-      <c r="L64" t="s" s="2">
-        <v>495</v>
-      </c>
-      <c r="M64" t="s" s="2">
-        <v>478</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -9436,7 +9397,7 @@
         <v>78</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>486</v>
+        <v>491</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>79</v>
@@ -9451,31 +9412,29 @@
         <v>101</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>490</v>
+        <v>495</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>482</v>
+        <v>496</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>491</v>
+        <v>497</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>484</v>
+        <v>78</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>78</v>
       </c>
     </row>
-    <row r="65">
+    <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>486</v>
-      </c>
-      <c r="C65" t="s" s="2">
-        <v>497</v>
-      </c>
+        <v>498</v>
+      </c>
+      <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
         <v>78</v>
       </c>
@@ -9484,28 +9443,30 @@
         <v>79</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H65" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="I65" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>498</v>
+        <v>177</v>
       </c>
       <c r="L65" t="s" s="2">
         <v>499</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>478</v>
+        <v>500</v>
       </c>
       <c r="N65" s="2"/>
-      <c r="O65" s="2"/>
+      <c r="O65" t="s" s="2">
+        <v>501</v>
+      </c>
       <c r="P65" t="s" s="2">
         <v>78</v>
       </c>
@@ -9553,7 +9514,7 @@
         <v>78</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>486</v>
+        <v>498</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>79</v>
@@ -9568,31 +9529,29 @@
         <v>101</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>490</v>
+        <v>502</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>482</v>
+        <v>503</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>491</v>
+        <v>504</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>484</v>
+        <v>78</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>78</v>
       </c>
     </row>
-    <row r="66">
+    <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>500</v>
+        <v>505</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>486</v>
-      </c>
-      <c r="C66" t="s" s="2">
-        <v>501</v>
-      </c>
+        <v>505</v>
+      </c>
+      <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
         <v>78</v>
       </c>
@@ -9601,25 +9560,25 @@
         <v>79</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H66" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="I66" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>494</v>
+        <v>506</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>502</v>
+        <v>507</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>478</v>
+        <v>508</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -9670,7 +9629,7 @@
         <v>78</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>486</v>
+        <v>505</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>79</v>
@@ -9685,27 +9644,27 @@
         <v>101</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>490</v>
+        <v>509</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>482</v>
+        <v>510</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>491</v>
+        <v>511</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>484</v>
+        <v>78</v>
       </c>
       <c r="AO66" t="s" s="2">
-        <v>78</v>
+        <v>512</v>
       </c>
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>503</v>
+        <v>513</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>503</v>
+        <v>513</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9728,15 +9687,17 @@
         <v>78</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>504</v>
+        <v>514</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>505</v>
+        <v>515</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>506</v>
-      </c>
-      <c r="N67" s="2"/>
+        <v>516</v>
+      </c>
+      <c r="N67" t="s" s="2">
+        <v>517</v>
+      </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
         <v>78</v>
@@ -9785,7 +9746,7 @@
         <v>78</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>503</v>
+        <v>513</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>79</v>
@@ -9800,372 +9761,23 @@
         <v>101</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>507</v>
+        <v>518</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>508</v>
+        <v>132</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>509</v>
+        <v>519</v>
       </c>
       <c r="AN67" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AO67" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="68" hidden="true">
-      <c r="A68" t="s" s="2">
-        <v>510</v>
-      </c>
-      <c r="B68" t="s" s="2">
-        <v>510</v>
-      </c>
-      <c r="C68" s="2"/>
-      <c r="D68" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E68" s="2"/>
-      <c r="F68" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G68" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H68" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I68" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J68" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="K68" t="s" s="2">
-        <v>177</v>
-      </c>
-      <c r="L68" t="s" s="2">
-        <v>511</v>
-      </c>
-      <c r="M68" t="s" s="2">
-        <v>512</v>
-      </c>
-      <c r="N68" s="2"/>
-      <c r="O68" t="s" s="2">
-        <v>513</v>
-      </c>
-      <c r="P68" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q68" s="2"/>
-      <c r="R68" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S68" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T68" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U68" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V68" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W68" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X68" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y68" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z68" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA68" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB68" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC68" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD68" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE68" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF68" t="s" s="2">
-        <v>510</v>
-      </c>
-      <c r="AG68" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH68" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI68" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ68" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK68" t="s" s="2">
-        <v>514</v>
-      </c>
-      <c r="AL68" t="s" s="2">
-        <v>515</v>
-      </c>
-      <c r="AM68" t="s" s="2">
-        <v>516</v>
-      </c>
-      <c r="AN68" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO68" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="69" hidden="true">
-      <c r="A69" t="s" s="2">
-        <v>517</v>
-      </c>
-      <c r="B69" t="s" s="2">
-        <v>517</v>
-      </c>
-      <c r="C69" s="2"/>
-      <c r="D69" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E69" s="2"/>
-      <c r="F69" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G69" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H69" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I69" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J69" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="K69" t="s" s="2">
-        <v>518</v>
-      </c>
-      <c r="L69" t="s" s="2">
-        <v>519</v>
-      </c>
-      <c r="M69" t="s" s="2">
-        <v>520</v>
-      </c>
-      <c r="N69" s="2"/>
-      <c r="O69" s="2"/>
-      <c r="P69" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q69" s="2"/>
-      <c r="R69" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S69" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T69" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U69" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V69" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W69" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X69" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y69" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z69" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA69" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB69" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC69" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD69" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE69" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF69" t="s" s="2">
-        <v>517</v>
-      </c>
-      <c r="AG69" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH69" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI69" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ69" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK69" t="s" s="2">
-        <v>521</v>
-      </c>
-      <c r="AL69" t="s" s="2">
-        <v>522</v>
-      </c>
-      <c r="AM69" t="s" s="2">
-        <v>523</v>
-      </c>
-      <c r="AN69" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO69" t="s" s="2">
-        <v>524</v>
-      </c>
-    </row>
-    <row r="70" hidden="true">
-      <c r="A70" t="s" s="2">
-        <v>525</v>
-      </c>
-      <c r="B70" t="s" s="2">
-        <v>525</v>
-      </c>
-      <c r="C70" s="2"/>
-      <c r="D70" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E70" s="2"/>
-      <c r="F70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G70" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H70" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I70" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J70" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="K70" t="s" s="2">
-        <v>526</v>
-      </c>
-      <c r="L70" t="s" s="2">
-        <v>527</v>
-      </c>
-      <c r="M70" t="s" s="2">
-        <v>528</v>
-      </c>
-      <c r="N70" t="s" s="2">
-        <v>529</v>
-      </c>
-      <c r="O70" s="2"/>
-      <c r="P70" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q70" s="2"/>
-      <c r="R70" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S70" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T70" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U70" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V70" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W70" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X70" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y70" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z70" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA70" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB70" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC70" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD70" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE70" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF70" t="s" s="2">
-        <v>525</v>
-      </c>
-      <c r="AG70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH70" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI70" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ70" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK70" t="s" s="2">
-        <v>530</v>
-      </c>
-      <c r="AL70" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="AM70" t="s" s="2">
-        <v>531</v>
-      </c>
-      <c r="AN70" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO70" t="s" s="2">
         <v>78</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AO70">
+  <autoFilter ref="A1:AO67">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -10175,7 +9787,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI69">
+  <conditionalFormatting sqref="A2:AI66">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>
